--- a/samples/Trial_Balance_VM_Aug-26.xlsx
+++ b/samples/Trial_Balance_VM_Aug-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>17331598.35</v>
+        <v>1710678.11</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>28932.75</v>
+        <v>26675.12</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>9422212.8</v>
+        <v>9014805.8</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>558620.85</v>
+        <v>602696.43</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>504208.8</v>
+        <v>473473.85</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>1092937.5</v>
+        <v>1108420.78</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D13">
-        <v>1863000</v>
+        <v>1620000</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D14">
-        <v>4744895.85</v>
+        <v>4671956.51</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D15">
-        <v>-1805683.5</v>
+        <v>-1727607.56</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D16">
-        <v>286140</v>
+        <v>290193.65</v>
       </c>
     </row>
     <row r="17">
@@ -590,7 +590,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D17">
-        <v>-2749020.75</v>
+        <v>-2655204.96</v>
       </c>
     </row>
     <row r="18">
@@ -604,7 +604,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D18">
-        <v>-1463325</v>
+        <v>-1361518.75</v>
       </c>
     </row>
     <row r="19">
@@ -618,7 +618,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D19">
-        <v>-807056.25</v>
+        <v>-654791.64</v>
       </c>
     </row>
     <row r="20">
@@ -632,7 +632,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D20">
-        <v>-539276.4</v>
+        <v>-525880.91</v>
       </c>
     </row>
     <row r="21">
@@ -646,7 +646,7 @@
         <v>Equity</v>
       </c>
       <c r="D21">
-        <v>-11306250</v>
+        <v>-2500000</v>
       </c>
     </row>
     <row r="22">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-6036000</v>
+        <v>-500000</v>
       </c>
     </row>
     <row r="23">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-3100597.5</v>
+        <v>-3144522.63</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-28482225</v>
+        <v>-23108578.55</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-4575000</v>
+        <v>-3650000</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Other Income</v>
       </c>
       <c r="D26">
-        <v>-179193.75</v>
+        <v>-145385.86</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D27">
-        <v>10324631.25</v>
+        <v>8376717.49</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>8895881.25</v>
+        <v>7217524.99</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>827475</v>
+        <v>671358.05</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>1168312.5</v>
+        <v>947890.88</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>909375</v>
+        <v>737806.25</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>1493606.25</v>
+        <v>1211812.54</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>498862.5</v>
+        <v>404743.78</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>1092937.5</v>
+        <v>886736.63</v>
       </c>
     </row>
     <row r="35">

--- a/samples/Trial_Balance_VM_Aug-26.xlsx
+++ b/samples/Trial_Balance_VM_Aug-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>1710678.11</v>
+        <v>3461304.31</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>Equity</v>
       </c>
       <c r="D21">
-        <v>-2500000</v>
+        <v>-4000000</v>
       </c>
     </row>
     <row r="22">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-500000</v>
+        <v>-1000000</v>
       </c>
     </row>
     <row r="23">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-3144522.63</v>
+        <v>-6144522.63</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-23108578.55</v>
+        <v>-4621573.68</v>
       </c>
     </row>
     <row r="25">
@@ -716,7 +716,7 @@
         <v>Other Income</v>
       </c>
       <c r="D26">
-        <v>-145385.86</v>
+        <v>-38259.44</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D27">
-        <v>8376717.49</v>
+        <v>2090364.84</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>7217524.99</v>
+        <v>1806286.61</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>671358.05</v>
+        <v>167839.51</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>947890.88</v>
+        <v>236972.72</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>737806.25</v>
+        <v>182550</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>1211812.54</v>
+        <v>304858.5</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>404743.78</v>
+        <v>99276.78</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>886736.63</v>
+        <v>221684.16</v>
       </c>
     </row>
     <row r="35">

--- a/samples/Trial_Balance_VM_Aug-26.xlsx
+++ b/samples/Trial_Balance_VM_Aug-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>3461304.31</v>
+        <v>5790739.44</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-6144522.63</v>
+        <v>-7322205.14</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-4621573.68</v>
+        <v>-5773326.3</v>
       </c>
     </row>
     <row r="25">
